--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.16516489340144</v>
+        <v>6.526839295177734</v>
       </c>
       <c r="D2" t="n">
-        <v>39.96105091558251</v>
+        <v>6.493670773782158</v>
       </c>
       <c r="E2" t="n">
-        <v>6.213467123123434</v>
+        <v>1.009688407507558</v>
       </c>
       <c r="F2" t="n">
-        <v>5.023205179812862</v>
+        <v>0.8162708417195902</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.21921752198852</v>
+        <v>5.398122847323134</v>
       </c>
       <c r="D3" t="n">
-        <v>25.84320062746691</v>
+        <v>4.199520101963373</v>
       </c>
       <c r="E3" t="n">
-        <v>6.213467123123434</v>
+        <v>1.009688407507558</v>
       </c>
       <c r="F3" t="n">
-        <v>5.023205179812862</v>
+        <v>0.8162708417195902</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.33036418060069</v>
+        <v>4.441184179347611</v>
       </c>
       <c r="D4" t="n">
-        <v>31.61530099405103</v>
+        <v>5.137486411533293</v>
       </c>
       <c r="E4" t="n">
-        <v>6.213467123123434</v>
+        <v>1.009688407507558</v>
       </c>
       <c r="F4" t="n">
-        <v>5.023205179812862</v>
+        <v>0.8162708417195902</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.7820368368104</v>
+        <v>3.86458098598169</v>
       </c>
       <c r="D5" t="n">
-        <v>32.94867325575175</v>
+        <v>5.35415940405966</v>
       </c>
       <c r="E5" t="n">
-        <v>6.213467123123434</v>
+        <v>1.009688407507558</v>
       </c>
       <c r="F5" t="n">
-        <v>5.023205179812862</v>
+        <v>0.8162708417195902</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
